--- a/data/trans_dic/P33B_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R2-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 14,95</t>
+          <t>8,71; 14,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,32</t>
+          <t>12,22; 17,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,29</t>
+          <t>11,31; 15,35</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,41</t>
+          <t>9,0; 15,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,2; 21,58</t>
+          <t>15,95; 22,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 17,27</t>
+          <t>13,14; 17,41</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 19,85</t>
+          <t>14,42; 21,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,22; 32,18</t>
+          <t>21,25; 31,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 21,63</t>
+          <t>17,89; 23,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,32</t>
+          <t>14,07; 18,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 21,73</t>
+          <t>18,72; 23,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 18,61</t>
+          <t>16,79; 19,74</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,33; 20,48</t>
+          <t>11,93; 18,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,83; 30,22</t>
+          <t>27,0; 32,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 25,03</t>
+          <t>21,7; 25,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 10,88</t>
+          <t>1,86; 10,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,89; 26,16</t>
+          <t>20,91; 25,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,55; 21,37</t>
+          <t>17,31; 21,78</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,79</t>
+          <t>13,0; 15,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,81; 22,42</t>
+          <t>21,54; 23,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,37</t>
+          <t>17,69; 19,42</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60168</t>
+          <t>63370</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64802</t>
+          <t>72268</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124970</t>
+          <t>135638</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46945; 75522</t>
+          <t>47971; 80158</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53755; 77512</t>
+          <t>59659; 86018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108371; 145645</t>
+          <t>117491; 159521</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69467</t>
+          <t>79412</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>136930</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42425; 69678</t>
+          <t>43491; 73250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58147; 82544</t>
+          <t>67480; 93207</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107772; 144151</t>
+          <t>119085; 157812</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79201</t>
+          <t>85520</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44334</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123535</t>
+          <t>135549</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31016; 132636</t>
+          <t>68011; 100711</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35423; 53709</t>
+          <t>39839; 59943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58486; 180678</t>
+          <t>117905; 155003</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>165386</t>
+          <t>183161</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>161748</t>
+          <t>180985</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>364147</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142711; 189539</t>
+          <t>159254; 208436</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92835; 212504</t>
+          <t>161247; 201138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225931; 374587</t>
+          <t>334584; 393455</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77816</t>
+          <t>84860</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>218863</t>
+          <t>244957</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296680</t>
+          <t>329817</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63191; 97091</t>
+          <t>67607; 104899</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>166396; 253584</t>
+          <t>224126; 268000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237969; 328663</t>
+          <t>303207; 359555</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>177719</t>
+          <t>197781</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188425</t>
+          <t>209087</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3567; 26168</t>
+          <t>4416; 24072</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>159028; 199193</t>
+          <t>176544; 218604</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165860; 214102</t>
+          <t>187204; 235503</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>448881</t>
+          <t>485736</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>736933</t>
+          <t>825431</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1185814</t>
+          <t>1311168</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>351024; 499304</t>
+          <t>447278; 527152</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>600872; 801638</t>
+          <t>782979; 866477</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1024802; 1276728</t>
+          <t>1251953; 1374055</t>
         </is>
       </c>
     </row>
